--- a/data/TestMultiKey.xlsx
+++ b/data/TestMultiKey.xlsx
@@ -488,202 +488,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>map&lt;string,string&gt;</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>map&lt;string,string&gt;</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>repeated { uint32 key; uint32 value }</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>idx</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>multi key</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>multi key</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>multi key</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>fk:Test</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>gfk:Test</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="F5" t="inlineStr">
         <is>
